--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DDV_HRM-2031-0320/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Outer Radius</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Inner Radius</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -470,28 +460,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.52147</v>
+        <v>16.88498</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51817</v>
+        <v>16.521</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81516</v>
-      </c>
-      <c r="F2" t="n">
-        <v>53.70938</v>
+        <v>16.81125</v>
       </c>
       <c r="G2" t="n">
-        <v>42.03428</v>
+        <v>0.04973</v>
       </c>
       <c r="H2" t="n">
-        <v>84.34536</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.04912</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.79229</v>
+        <v>1.81268</v>
       </c>
     </row>
     <row r="3">
@@ -501,28 +482,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.84709</v>
+        <v>17.11172</v>
       </c>
       <c r="D3" t="n">
-        <v>16.61006</v>
+        <v>16.59245</v>
       </c>
       <c r="E3" t="n">
-        <v>16.52615</v>
+        <v>16.94511</v>
       </c>
       <c r="F3" t="n">
-        <v>55.75531</v>
+        <v>42.40478</v>
       </c>
       <c r="G3" t="n">
-        <v>41.5352</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>85.31106</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.05044</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.76739</v>
+        <v>1.82396</v>
       </c>
     </row>
     <row r="4">
@@ -531,29 +506,25 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>16.5638</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>16.68541</v>
+        <v>16.30209</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72249</v>
+        <v>16.52432</v>
       </c>
       <c r="F4" t="n">
-        <v>54.92399</v>
+        <v>42.53389</v>
       </c>
       <c r="G4" t="n">
-        <v>42.38084</v>
+        <v>0.05077</v>
       </c>
       <c r="H4" t="n">
-        <v>83.80449</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05097</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.76275</v>
+        <v>1.82373</v>
       </c>
     </row>
     <row r="5">
@@ -562,29 +533,25 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>16.60988</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,5</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>16.50786</v>
+        <v>16.5877</v>
       </c>
       <c r="E5" t="n">
-        <v>16.57634</v>
+        <v>16.78346</v>
       </c>
       <c r="F5" t="n">
-        <v>55.72338</v>
+        <v>41.95343</v>
       </c>
       <c r="G5" t="n">
-        <v>42.12718</v>
+        <v>0.05111</v>
       </c>
       <c r="H5" t="n">
-        <v>83.10632</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.05057</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.81276</v>
+        <v>1.79319</v>
       </c>
     </row>
     <row r="6">
@@ -594,28 +561,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.02543</v>
+        <v>17.06246</v>
       </c>
       <c r="D6" t="n">
-        <v>16.33189</v>
+        <v>16.5268</v>
       </c>
       <c r="E6" t="n">
-        <v>16.72803</v>
+        <v>16.672</v>
       </c>
       <c r="F6" t="n">
-        <v>54.18895</v>
+        <v>42.0833</v>
       </c>
       <c r="G6" t="n">
-        <v>42.1269</v>
-      </c>
-      <c r="H6" t="n">
-        <v>86.59707</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.05175</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.84505</v>
+        <v>0.05029</v>
+      </c>
+      <c r="H6" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +586,24 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.54893</v>
+        <v>16.74358</v>
       </c>
       <c r="D7" t="n">
-        <v>16.76431</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.52559</v>
+        <v>16.55818</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 16.48 </t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>54.03173</v>
+        <v>43.14705</v>
       </c>
       <c r="G7" t="n">
-        <v>41.65855</v>
+        <v>0.0495</v>
       </c>
       <c r="H7" t="n">
-        <v>85.20151</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.04974</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.81313</v>
+        <v>1.8297</v>
       </c>
     </row>
     <row r="8">
@@ -656,28 +613,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.39665</v>
+        <v>16.82123</v>
       </c>
       <c r="D8" t="n">
-        <v>16.6911</v>
+        <v>16.22973</v>
       </c>
       <c r="E8" t="n">
-        <v>17.00157</v>
+        <v>16.77222</v>
       </c>
       <c r="F8" t="n">
-        <v>55.38775</v>
+        <v>42.14326</v>
       </c>
       <c r="G8" t="n">
-        <v>43.18071</v>
+        <v>0.05021</v>
       </c>
       <c r="H8" t="n">
-        <v>84.19495999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.04968</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.82827</v>
+        <v>1.82087</v>
       </c>
     </row>
     <row r="9">
@@ -687,28 +638,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.75679</v>
+        <v>16.82929</v>
       </c>
       <c r="D9" t="n">
-        <v>16.45814</v>
+        <v>16.54342</v>
       </c>
       <c r="E9" t="n">
-        <v>16.3619</v>
+        <v>16.68286</v>
       </c>
       <c r="F9" t="n">
-        <v>54.57955</v>
+        <v>42.80998</v>
       </c>
       <c r="G9" t="n">
-        <v>41.22725</v>
+        <v>0.05079</v>
       </c>
       <c r="H9" t="n">
-        <v>84.24053000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0506</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.8043</v>
+        <v>1.79717</v>
       </c>
     </row>
     <row r="10">
@@ -718,67 +663,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.64578</v>
+        <v>16.87114</v>
       </c>
       <c r="D10" t="n">
-        <v>16.44725</v>
+        <v>16.2761</v>
       </c>
       <c r="E10" t="n">
-        <v>16.08795</v>
+        <v>16.5714</v>
       </c>
       <c r="F10" t="n">
-        <v>55.06003</v>
+        <v>41.94589</v>
       </c>
       <c r="G10" t="n">
-        <v>41.51937</v>
+        <v>0.05001</v>
       </c>
       <c r="H10" t="n">
-        <v>84.66046</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.05059</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.81328</v>
+        <v>1.84001</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Outer Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Inner Radius</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Diameter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -792,32 +701,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 2</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.83815</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>16.54982</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.42261</v>
-      </c>
-      <c r="F12" t="n">
-        <v>55.50223</v>
-      </c>
-      <c r="G12" t="n">
-        <v>41.57991</v>
-      </c>
-      <c r="H12" t="n">
-        <v>83.04859999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.04954</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.7713</v>
+        <v>1.14014</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +718,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.66316</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>16.48509</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.79291</v>
-      </c>
-      <c r="F13" t="n">
-        <v>54.7829</v>
-      </c>
-      <c r="G13" t="n">
-        <v>42.09594</v>
-      </c>
-      <c r="H13" t="n">
-        <v>86.67288000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05104</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.77827</v>
+        <v>1.10456</v>
       </c>
     </row>
     <row r="14">
@@ -858,28 +731,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.51001</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>16.37317</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.44163</v>
-      </c>
-      <c r="F14" t="n">
-        <v>54.63078</v>
-      </c>
-      <c r="G14" t="n">
-        <v>42.32035</v>
-      </c>
-      <c r="H14" t="n">
-        <v>85.14395</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0507</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.82542</v>
+        <v>1.13503</v>
       </c>
     </row>
     <row r="15">
@@ -889,28 +744,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.46306</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>16.12296</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.58205</v>
-      </c>
-      <c r="F15" t="n">
-        <v>55.14348</v>
-      </c>
-      <c r="G15" t="n">
-        <v>42.1309</v>
-      </c>
-      <c r="H15" t="n">
-        <v>84.72984</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.05072</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.81323</v>
+        <v>1.09365</v>
       </c>
     </row>
     <row r="16">
@@ -920,28 +757,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.72618</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>16.44294</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.61791</v>
-      </c>
-      <c r="F16" t="n">
-        <v>54.1269</v>
-      </c>
-      <c r="G16" t="n">
-        <v>42.01409</v>
-      </c>
-      <c r="H16" t="n">
-        <v>85.12123</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.05149</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.79615</v>
+        <v>1.12334</v>
       </c>
     </row>
     <row r="17">
@@ -951,28 +770,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.67661</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>16.92718</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.78733</v>
-      </c>
-      <c r="F17" t="n">
-        <v>54.92137</v>
-      </c>
-      <c r="G17" t="n">
-        <v>42.38838</v>
-      </c>
-      <c r="H17" t="n">
-        <v>84.89895</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.05119</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.81506</v>
+        <v>1.12044</v>
       </c>
     </row>
     <row r="18">
@@ -982,28 +783,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.51994</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>16.55787</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.08232</v>
-      </c>
-      <c r="F18" t="n">
-        <v>55.11662</v>
-      </c>
-      <c r="G18" t="n">
-        <v>42.37446</v>
-      </c>
-      <c r="H18" t="n">
-        <v>84.19029</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.05066</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.77035</v>
+        <v>1.1059</v>
       </c>
     </row>
     <row r="19">
@@ -1013,28 +796,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.89082</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.97263</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.66525</v>
-      </c>
-      <c r="F19" t="n">
-        <v>55.0228</v>
-      </c>
-      <c r="G19" t="n">
-        <v>42.58467</v>
-      </c>
-      <c r="H19" t="n">
-        <v>84.26133</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.05077</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.81047</v>
+        <v>1.07992</v>
       </c>
     </row>
     <row r="20">
@@ -1044,258 +809,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.6951</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16.62634</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.49736</v>
-      </c>
-      <c r="F20" t="n">
-        <v>54.82678</v>
-      </c>
-      <c r="G20" t="n">
-        <v>41.71245</v>
-      </c>
-      <c r="H20" t="n">
-        <v>84.60786</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.05184</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.80712</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>16.31745</v>
-      </c>
-      <c r="D22" t="n">
-        <v>15.93886</v>
-      </c>
-      <c r="E22" t="n">
-        <v>16.52524</v>
-      </c>
-      <c r="F22" t="n">
-        <v>21.60607</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.52735</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>16.48298</v>
-      </c>
-      <c r="D23" t="n">
-        <v>16.18141</v>
-      </c>
-      <c r="E23" t="n">
-        <v>16.35806</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21.8223</v>
-      </c>
-      <c r="G23" t="n">
-        <v>33.81619</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>16.57952</v>
-      </c>
-      <c r="D24" t="n">
-        <v>15.75754</v>
-      </c>
-      <c r="E24" t="n">
-        <v>15.93907</v>
-      </c>
-      <c r="F24" t="n">
-        <v>21.85598</v>
-      </c>
-      <c r="G24" t="n">
-        <v>33.78837</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>16.37632</v>
-      </c>
-      <c r="D25" t="n">
-        <v>16.17556</v>
-      </c>
-      <c r="E25" t="n">
-        <v>16.50705</v>
-      </c>
-      <c r="F25" t="n">
-        <v>21.80708</v>
-      </c>
-      <c r="G25" t="n">
-        <v>34.51703</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>16.73837</v>
-      </c>
-      <c r="D26" t="n">
-        <v>15.85428</v>
-      </c>
-      <c r="E26" t="n">
-        <v>16.2127</v>
-      </c>
-      <c r="F26" t="n">
-        <v>21.83935</v>
-      </c>
-      <c r="G26" t="n">
-        <v>34.68145</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>16.7833</v>
-      </c>
-      <c r="D27" t="n">
-        <v>15.92662</v>
-      </c>
-      <c r="E27" t="n">
-        <v>16.2676</v>
-      </c>
-      <c r="F27" t="n">
-        <v>21.60921</v>
-      </c>
-      <c r="G27" t="n">
-        <v>33.789</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>16.55642</v>
-      </c>
-      <c r="D28" t="n">
-        <v>16.07191</v>
-      </c>
-      <c r="E28" t="n">
-        <v>16.54194</v>
-      </c>
-      <c r="F28" t="n">
-        <v>21.34554</v>
-      </c>
-      <c r="G28" t="n">
-        <v>34.03132</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>16.77517</v>
-      </c>
-      <c r="D29" t="n">
-        <v>15.76416</v>
-      </c>
-      <c r="E29" t="n">
-        <v>16.15311</v>
-      </c>
-      <c r="F29" t="n">
-        <v>22.03735</v>
-      </c>
-      <c r="G29" t="n">
-        <v>34.02527</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>16.59185</v>
-      </c>
-      <c r="D30" t="n">
-        <v>16.01672</v>
-      </c>
-      <c r="E30" t="n">
-        <v>16.58767</v>
-      </c>
-      <c r="F30" t="n">
-        <v>21.76451</v>
-      </c>
-      <c r="G30" t="n">
-        <v>32.76162</v>
+        <v>1.11078</v>
       </c>
     </row>
   </sheetData>
